--- a/ONCHO/Impact Assessments/Nigeria/2025/river states ia/ng_oncho_stop_2507_1_site_ia_rs.xlsx
+++ b/ONCHO/Impact Assessments/Nigeria/2025/river states ia/ng_oncho_stop_2507_1_site_ia_rs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Nigeria\2025\river states\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Nigeria\2025\river states ia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6556AE6E-A997-4C2D-9886-3106D95A0F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDD4DB8-DE88-46D2-B0AF-F4F15205E1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -392,9 +392,6 @@
     <t>${c_cluster_name}</t>
   </si>
   <si>
-    <t>ng_oncho_stop_2507_1_site_ia_rs</t>
-  </si>
-  <si>
     <t>. &gt; 1970 and . &lt;= 2025</t>
   </si>
   <si>
@@ -794,7 +791,10 @@
     <t>RIV_OPN_M_055</t>
   </si>
   <si>
-    <t>(River State 2025 July) - 1. Site Form</t>
+    <t>(River State 2025 July) - 1. Site Form V2</t>
+  </si>
+  <si>
+    <t>ng_oncho_stop_2507_1_site_ia_rs_v2</t>
   </si>
 </sst>
 </file>
@@ -1661,7 +1661,7 @@
         <v>70</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>71</v>
@@ -2017,10 +2017,10 @@
         <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2028,13 +2028,13 @@
         <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2042,13 +2042,13 @@
         <v>85</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2056,13 +2056,13 @@
         <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2070,13 +2070,13 @@
         <v>85</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2084,13 +2084,13 @@
         <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2098,13 +2098,13 @@
         <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2112,13 +2112,13 @@
         <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2126,13 +2126,13 @@
         <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2140,13 +2140,13 @@
         <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2154,13 +2154,13 @@
         <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2168,13 +2168,13 @@
         <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2182,13 +2182,13 @@
         <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2199,13 +2199,13 @@
         <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2213,13 +2213,13 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E39" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2227,13 +2227,13 @@
         <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2241,13 +2241,13 @@
         <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2255,13 +2255,13 @@
         <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2269,13 +2269,13 @@
         <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2283,13 +2283,13 @@
         <v>86</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2297,13 +2297,13 @@
         <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2311,13 +2311,13 @@
         <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2325,13 +2325,13 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2339,13 +2339,13 @@
         <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2353,13 +2353,13 @@
         <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2367,13 +2367,13 @@
         <v>86</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2381,13 +2381,13 @@
         <v>86</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C51" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2395,13 +2395,13 @@
         <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C52" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2409,13 +2409,13 @@
         <v>86</v>
       </c>
       <c r="B53" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C53" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E53" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2423,13 +2423,13 @@
         <v>86</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2437,13 +2437,13 @@
         <v>86</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E55" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2451,13 +2451,13 @@
         <v>86</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E56" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2465,13 +2465,13 @@
         <v>86</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2479,13 +2479,13 @@
         <v>86</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E58" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2493,13 +2493,13 @@
         <v>86</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E59" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2507,13 +2507,13 @@
         <v>86</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E60" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2521,13 +2521,13 @@
         <v>86</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C61" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E61" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2535,13 +2535,13 @@
         <v>86</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C62" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E62" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2549,13 +2549,13 @@
         <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E63" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2563,13 +2563,13 @@
         <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C64" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E64" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2577,13 +2577,13 @@
         <v>86</v>
       </c>
       <c r="B65" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C65" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E65" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2591,13 +2591,13 @@
         <v>86</v>
       </c>
       <c r="B66" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C66" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2605,13 +2605,13 @@
         <v>86</v>
       </c>
       <c r="B67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E67" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2619,13 +2619,13 @@
         <v>86</v>
       </c>
       <c r="B68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2633,13 +2633,13 @@
         <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C69" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E69" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2647,13 +2647,13 @@
         <v>86</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C70" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E70" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2661,13 +2661,13 @@
         <v>86</v>
       </c>
       <c r="B71" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C71" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E71" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2675,13 +2675,13 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C72" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E72" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2689,13 +2689,13 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E73" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2703,13 +2703,13 @@
         <v>86</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C74" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E74" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2717,13 +2717,13 @@
         <v>86</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E75" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2731,13 +2731,13 @@
         <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E76" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2745,13 +2745,13 @@
         <v>86</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E77" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2759,13 +2759,13 @@
         <v>86</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E78" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2773,13 +2773,13 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E79" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2787,13 +2787,13 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2801,13 +2801,13 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C81" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E81" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2815,13 +2815,13 @@
         <v>86</v>
       </c>
       <c r="B82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E82" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2829,13 +2829,13 @@
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C83" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E83" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2843,13 +2843,13 @@
         <v>86</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E84" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2857,13 +2857,13 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C85" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E85" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2871,13 +2871,13 @@
         <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C86" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E86" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2885,13 +2885,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E87" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2899,13 +2899,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C88" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E88" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2913,13 +2913,13 @@
         <v>86</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E89" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2927,13 +2927,13 @@
         <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C90" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E90" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2941,13 +2941,13 @@
         <v>86</v>
       </c>
       <c r="B91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E91" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2955,13 +2955,13 @@
         <v>86</v>
       </c>
       <c r="B92" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C92" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E92" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2969,13 +2969,13 @@
         <v>86</v>
       </c>
       <c r="B93" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C93" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E93" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2983,13 +2983,13 @@
         <v>86</v>
       </c>
       <c r="B94" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C94" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E94" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2997,13 +2997,13 @@
         <v>86</v>
       </c>
       <c r="B95" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C95" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E95" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3011,13 +3011,13 @@
         <v>86</v>
       </c>
       <c r="B96" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C96" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3025,13 +3025,13 @@
         <v>86</v>
       </c>
       <c r="B97" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C97" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E97" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -3039,13 +3039,13 @@
         <v>108</v>
       </c>
       <c r="B99" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C99" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F99" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3053,13 +3053,13 @@
         <v>108</v>
       </c>
       <c r="B100" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C100" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3067,13 +3067,13 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C101" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3081,13 +3081,13 @@
         <v>108</v>
       </c>
       <c r="B102" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C102" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F102" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3095,13 +3095,13 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C103" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F103" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3109,13 +3109,13 @@
         <v>108</v>
       </c>
       <c r="B104" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C104" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F104" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3123,13 +3123,13 @@
         <v>108</v>
       </c>
       <c r="B105" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C105" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F105" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3137,13 +3137,13 @@
         <v>108</v>
       </c>
       <c r="B106" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C106" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F106" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3151,13 +3151,13 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C107" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F107" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3165,13 +3165,13 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C108" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F108" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3179,13 +3179,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C109" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F109" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3193,13 +3193,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C110" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F110" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3207,13 +3207,13 @@
         <v>108</v>
       </c>
       <c r="B111" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C111" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F111" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3221,13 +3221,13 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C112" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F112" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3235,13 +3235,13 @@
         <v>108</v>
       </c>
       <c r="B113" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C113" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F113" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3249,13 +3249,13 @@
         <v>108</v>
       </c>
       <c r="B114" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C114" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F114" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -3263,13 +3263,13 @@
         <v>108</v>
       </c>
       <c r="B115" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C115" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F115" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3277,13 +3277,13 @@
         <v>108</v>
       </c>
       <c r="B116" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C116" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3291,13 +3291,13 @@
         <v>108</v>
       </c>
       <c r="B117" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C117" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F117" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3305,13 +3305,13 @@
         <v>108</v>
       </c>
       <c r="B118" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C118" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F118" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -3319,13 +3319,13 @@
         <v>108</v>
       </c>
       <c r="B119" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C119" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F119" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3333,13 +3333,13 @@
         <v>108</v>
       </c>
       <c r="B120" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C120" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F120" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3347,13 +3347,13 @@
         <v>108</v>
       </c>
       <c r="B121" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C121" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F121" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3361,13 +3361,13 @@
         <v>108</v>
       </c>
       <c r="B122" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C122" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F122" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3375,13 +3375,13 @@
         <v>108</v>
       </c>
       <c r="B123" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C123" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F123" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3389,13 +3389,13 @@
         <v>108</v>
       </c>
       <c r="B124" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C124" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F124" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3403,13 +3403,13 @@
         <v>108</v>
       </c>
       <c r="B125" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C125" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F125" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3417,13 +3417,13 @@
         <v>108</v>
       </c>
       <c r="B126" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C126" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F126" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3431,13 +3431,13 @@
         <v>108</v>
       </c>
       <c r="B127" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C127" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F127" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3445,13 +3445,13 @@
         <v>108</v>
       </c>
       <c r="B128" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C128" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F128" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3459,13 +3459,13 @@
         <v>108</v>
       </c>
       <c r="B129" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C129" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F129" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3473,13 +3473,13 @@
         <v>108</v>
       </c>
       <c r="B130" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C130" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F130" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3487,13 +3487,13 @@
         <v>108</v>
       </c>
       <c r="B131" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C131" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F131" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3501,13 +3501,13 @@
         <v>108</v>
       </c>
       <c r="B132" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C132" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F132" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -3515,13 +3515,13 @@
         <v>108</v>
       </c>
       <c r="B133" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C133" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F133" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3529,13 +3529,13 @@
         <v>108</v>
       </c>
       <c r="B134" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C134" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F134" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3543,13 +3543,13 @@
         <v>108</v>
       </c>
       <c r="B135" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C135" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F135" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3557,13 +3557,13 @@
         <v>108</v>
       </c>
       <c r="B136" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C136" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -3571,13 +3571,13 @@
         <v>108</v>
       </c>
       <c r="B137" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C137" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F137" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3585,13 +3585,13 @@
         <v>108</v>
       </c>
       <c r="B138" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C138" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F138" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3599,13 +3599,13 @@
         <v>108</v>
       </c>
       <c r="B139" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C139" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F139" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3613,13 +3613,13 @@
         <v>108</v>
       </c>
       <c r="B140" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C140" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F140" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -3627,13 +3627,13 @@
         <v>108</v>
       </c>
       <c r="B141" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C141" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F141" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -3641,13 +3641,13 @@
         <v>108</v>
       </c>
       <c r="B142" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C142" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F142" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3655,13 +3655,13 @@
         <v>108</v>
       </c>
       <c r="B143" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C143" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F143" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -3669,13 +3669,13 @@
         <v>108</v>
       </c>
       <c r="B144" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C144" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F144" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -3683,13 +3683,13 @@
         <v>108</v>
       </c>
       <c r="B145" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C145" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F145" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -3697,13 +3697,13 @@
         <v>108</v>
       </c>
       <c r="B146" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C146" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F146" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -3711,13 +3711,13 @@
         <v>108</v>
       </c>
       <c r="B147" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C147" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F147" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -3725,13 +3725,13 @@
         <v>108</v>
       </c>
       <c r="B148" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C148" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F148" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -3739,13 +3739,13 @@
         <v>108</v>
       </c>
       <c r="B149" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C149" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F149" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -3753,13 +3753,13 @@
         <v>108</v>
       </c>
       <c r="B150" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C150" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F150" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -3767,13 +3767,13 @@
         <v>108</v>
       </c>
       <c r="B151" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C151" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F151" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -3781,13 +3781,13 @@
         <v>108</v>
       </c>
       <c r="B152" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C152" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F152" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -3795,13 +3795,13 @@
         <v>108</v>
       </c>
       <c r="B153" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C153" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F153" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -3809,13 +3809,13 @@
         <v>108</v>
       </c>
       <c r="B154" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C154" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F154" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -3823,13 +3823,13 @@
         <v>108</v>
       </c>
       <c r="B155" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C155" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F155" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -3837,13 +3837,13 @@
         <v>108</v>
       </c>
       <c r="B156" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C156" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F156" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -3851,13 +3851,13 @@
         <v>108</v>
       </c>
       <c r="B157" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C157" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F157" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -3865,13 +3865,13 @@
         <v>108</v>
       </c>
       <c r="B158" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C158" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F158" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>253</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>119</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>112</v>
